--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.01124</v>
+        <v>17.39033</v>
       </c>
       <c r="D2" t="n">
-        <v>17.28731</v>
+        <v>16.97172</v>
       </c>
       <c r="E2" t="n">
-        <v>17.36505</v>
+        <v>17.0426</v>
       </c>
       <c r="F2" t="n">
-        <v>43.48282</v>
+        <v>44.24105</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05228</v>
+        <v>0.0517</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86823</v>
+        <v>1.8652</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.08753</v>
+        <v>17.34148</v>
       </c>
       <c r="D3" t="n">
-        <v>17.28392</v>
+        <v>16.99759</v>
       </c>
       <c r="E3" t="n">
-        <v>17.09419</v>
+        <v>17.14281</v>
       </c>
       <c r="F3" t="n">
-        <v>44.54009</v>
+        <v>42.78423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05168</v>
+        <v>0.05219</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82232</v>
+        <v>1.91812</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.38985</v>
+        <v>17.47421</v>
       </c>
       <c r="D4" t="n">
-        <v>17.1073</v>
+        <v>17.13508</v>
       </c>
       <c r="E4" t="n">
-        <v>17.00558</v>
+        <v>17.30125</v>
       </c>
       <c r="F4" t="n">
-        <v>42.62527</v>
+        <v>43.81532</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05209</v>
+        <v>0.05194</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91558</v>
+        <v>1.86929</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.29622</v>
+        <v>17.37874</v>
       </c>
       <c r="D5" t="n">
-        <v>16.95492</v>
+        <v>17.01265</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7503</v>
+        <v>17.19221</v>
       </c>
       <c r="F5" t="n">
-        <v>43.20825</v>
+        <v>44.59571</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05145</v>
+        <v>0.05178</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84875</v>
+        <v>1.86493</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.31865</v>
+        <v>17.57468</v>
       </c>
       <c r="D6" t="n">
-        <v>17.07142</v>
+        <v>17.09911</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8742</v>
+        <v>17.23718</v>
       </c>
       <c r="F6" t="n">
-        <v>42.80692</v>
+        <v>43.98413</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05196</v>
+        <v>0.05181</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86815</v>
+        <v>1.85994</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.16379</v>
+        <v>17.68805</v>
       </c>
       <c r="D7" t="n">
-        <v>16.85188</v>
+        <v>17.45052</v>
       </c>
       <c r="E7" t="n">
-        <v>16.98345</v>
+        <v>17.5479</v>
       </c>
       <c r="F7" t="n">
-        <v>44.49961</v>
+        <v>43.64255</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05154</v>
+        <v>0.0522</v>
       </c>
       <c r="H7" t="n">
-        <v>1.91159</v>
+        <v>1.8933</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.77525</v>
+        <v>17.28549</v>
       </c>
       <c r="D8" t="n">
-        <v>17.21505</v>
+        <v>17.0407</v>
       </c>
       <c r="E8" t="n">
-        <v>17.15661</v>
+        <v>17.27262</v>
       </c>
       <c r="F8" t="n">
-        <v>43.99742</v>
+        <v>44.1985</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05192</v>
+        <v>0.05153</v>
       </c>
       <c r="H8" t="n">
-        <v>1.88753</v>
+        <v>1.88372</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.65974</v>
+        <v>16.98303</v>
       </c>
       <c r="D9" t="n">
-        <v>17.03106</v>
+        <v>16.71032</v>
       </c>
       <c r="E9" t="n">
-        <v>17.08853</v>
+        <v>16.82253</v>
       </c>
       <c r="F9" t="n">
-        <v>44.08903</v>
+        <v>43.88364</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05171</v>
+        <v>0.05217</v>
       </c>
       <c r="H9" t="n">
-        <v>1.89542</v>
+        <v>1.8917</v>
       </c>
     </row>
     <row r="10">
@@ -650,482 +660,712 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.14562</v>
+        <v>17.24137</v>
       </c>
       <c r="D10" t="n">
-        <v>17.24467</v>
+        <v>16.94452</v>
       </c>
       <c r="E10" t="n">
-        <v>17.15178</v>
+        <v>16.98799</v>
       </c>
       <c r="F10" t="n">
-        <v>43.50246</v>
+        <v>44.01764</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05213</v>
+        <v>0.05206</v>
       </c>
       <c r="H10" t="n">
-        <v>1.86036</v>
+        <v>1.88126</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.49431</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.03867</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.09657</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.99893</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05177</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.87676</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6194499999999999</v>
+        <v>17.39216</v>
       </c>
       <c r="D12" t="n">
-        <v>1.15398</v>
+        <v>17.14029</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.23521</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.16337</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.83973</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.61674</v>
+        <v>17.22212</v>
       </c>
       <c r="D13" t="n">
-        <v>1.15733</v>
+        <v>16.73649</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.98842</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.79457</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.89135</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.61716</v>
+        <v>17.14098</v>
       </c>
       <c r="D14" t="n">
-        <v>1.14551</v>
+        <v>17.0144</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.09208</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.69617</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05223</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.86522</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.61286</v>
+        <v>17.3756</v>
       </c>
       <c r="D15" t="n">
-        <v>1.14089</v>
+        <v>17.27165</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.31376</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.91552</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05322</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.88133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62397</v>
+        <v>17.47511</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13843</v>
+        <v>17.06238</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.11043</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.91793</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05237</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.88001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.62579</v>
+        <v>17.23254</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1698</v>
+        <v>17.00903</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.10441</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.87257</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.84737</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6283</v>
+        <v>17.21594</v>
       </c>
       <c r="D18" t="n">
-        <v>1.14822</v>
+        <v>17.10012</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.13433</v>
+      </c>
+      <c r="F18" t="n">
+        <v>44.92673</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05216</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.86326</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.61936</v>
+        <v>17.21809</v>
       </c>
       <c r="D19" t="n">
-        <v>1.16075</v>
+        <v>16.96813</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.20731</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.55388</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05192</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.91257</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.62648</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.13455</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.62573</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.146</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.78372</v>
+        <v>0.63288</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08287</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.6302</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.98084</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.11084</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.007849999999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09604</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.13048</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.77302</v>
+        <v>0.61658</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08312</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.62447</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.99682</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11085</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09671</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13175</v>
+        <v>1.15143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.77336</v>
+        <v>0.61818</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08255</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.62053</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.98045</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11312</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.007860000000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09568</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.13155</v>
+        <v>1.15751</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.76723</v>
+        <v>0.6129599999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08352999999999999</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.63063</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.99721</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.11113</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.007820000000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09504</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.13132</v>
+        <v>1.14571</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74993</v>
+        <v>0.62376</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08119</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.6333299999999999</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.97445</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11427</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.007889999999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09588000000000001</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.13268</v>
+        <v>1.1418</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.76663</v>
+        <v>0.62446</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08308</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.61708</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.98783</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11256</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00783</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.0955</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12987</v>
+        <v>1.17031</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76272</v>
+        <v>0.6206199999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08114</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.63679</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.01319</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11069</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00791</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09662</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12606</v>
+        <v>1.1254</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.62913</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.14993</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.77764</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08389000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.62534</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.99916</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.11299</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00791</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09469</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.13079</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.77017</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08399</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.63013</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.98713</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11344</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09451</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.13133</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.78445</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08239</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.62463</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.98686</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11201</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09683</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.13252</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.78882</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08246000000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.61381</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.00856</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09694</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.13099</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.77787</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08411</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.64132</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.97575</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11239</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.008019999999999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09733</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12966</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.78254</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08381</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.61692</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.97824</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11182</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09575</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12737</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7671</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08341</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9895699999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09494</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.13081</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.78262</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.08313</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.62584</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.00532</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11403</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00774</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09778000000000001</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.13218</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="C38" t="n">
+        <v>0.77283</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08319</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.60964</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11281</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00805</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12673</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.77127</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.08165</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.64189</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.98591</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11348</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09548</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13031</v>
+      <c r="C39" t="n">
+        <v>0.76769</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.63725</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.01499</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11456</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09442</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1328</v>
       </c>
     </row>
   </sheetData>
